--- a/classifiche/Arese.xlsx
+++ b/classifiche/Arese.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t xml:space="preserve">Stagione</t>
   </si>
@@ -94,22 +94,22 @@
     <t xml:space="preserve">01:05.55</t>
   </si>
   <si>
+    <t xml:space="preserve">Mauro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:04.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommaso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MX-5 NB/FL 1.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mauro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01:04.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommaso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MX-5 NB/FL 1.8</t>
   </si>
   <si>
     <t xml:space="preserve">01:02.50</t>
@@ -741,16 +741,14 @@
       <c r="F5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -759,37 +757,33 @@
         <v>9</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
@@ -802,7 +796,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>32</v>
@@ -810,9 +804,7 @@
       <c r="F8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
@@ -825,17 +817,15 @@
         <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
@@ -856,9 +846,7 @@
       <c r="F10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
@@ -879,9 +867,7 @@
       <c r="F11" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
@@ -897,14 +883,12 @@
         <v>45</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
@@ -925,9 +909,7 @@
       <c r="F13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
@@ -971,9 +953,7 @@
       <c r="F15" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>24</v>
-      </c>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
@@ -994,9 +974,7 @@
       <c r="F16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="G16" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
